--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -468,9 +468,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>mrdmr7v8ss585</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Doctor and Dentist Appointments Scheduled</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Schedule doctor and dentist appointments. Bloodwork for Factor 5 and cavity are priorities</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -497,9 +497,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>mrdmsiosuupr9</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Pack for shark fishing to Jax</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pack up Thursday night for smooth transition Friday</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -526,9 +526,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>mrdmxnel4axgo</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Git and GitHub Training</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Complete the Git and GitHub training via NCEAS resources</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G5" t="str">
+        <v>When Time Allows</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -555,9 +555,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>mrdmyktkaxaoo</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Dive into NCEAS Professionals</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Look into the professionals that will be making up the NCEAS team, have fun facts ready, be the caring person</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G6" t="str">
+        <v>When Time Allows</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -584,9 +584,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>mrdn0d74e91gy</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Podcasts (2 Done and Listened To)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Create and Listen to 2 Podcasts via Podcast SOP and 2 separate articles</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>For research and overall knowledge of canals</v>
+      </c>
+      <c r="I7" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -613,9 +613,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>mrdn1lsf5aq0r</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Advance Lit Review</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Advance literature review with Consensus connection on PC Claude file</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E8" t="str">
+        <v>High</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -642,9 +642,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>mrdn36bh55y7k</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Gulf Coast States Canals</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Dive into datasets again regarding canals in the other Gulf States, or bite the bullet and start manually classifying</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E9" t="str">
+        <v>High</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Look into NHD and see if it is better for other states.</v>
+      </c>
+      <c r="I9" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -668,7 +668,7 @@
         <v>Look into NHD and see if it is better for other states.</v>
       </c>
       <c r="I9" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -668,7 +668,7 @@
         <v>Look into NHD and see if it is better for other states.</v>
       </c>
       <c r="I9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -671,9 +671,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>mrdn4qipfpglv</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Re-read NCEAS Proposal (Again)</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E10" t="str">
+        <v>High</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -700,9 +700,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>mrdn8rhcz67a4</v>
+      </c>
+      <c r="B11" t="str">
+        <v>AI Learnings</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Learn more about AI and some repositories and GitHub in general</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G11" t="str">
+        <v>When Time Allows</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -465,7 +465,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="3">
@@ -604,7 +604,7 @@
         <v>2026-07-09</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>When Time Allows</v>
       </c>
       <c r="H7" t="str">
         <v>For research and overall knowledge of canals</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -729,9 +729,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>mrdwwugr2bjqx</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Charlotte Distance Raster Map</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Charlotte distance on Rotunda and the Left side of the river</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="H12" t="str">
+        <v>Just below state park to bottom of rotunda</v>
+      </c>
+      <c r="I12" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -758,9 +758,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>mrdwxno6g24ly</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Brainstorm NCEAS ?s</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Ask 1-2 interesting questions of each scientist for a good promo video. Informed questions that are not too vague but still does not pin them in a corner they are not familiar with</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -787,9 +787,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>mrdwxxxvdijrl</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Cheat sheet for the NCEAS proposal</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Cheat sheet for the NCEAS proposal</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2026-07-22</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -816,9 +816,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>mrdwy7trwv2x3</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Admin@CHAWQ GitHub to host the HTML dashboards</v>
+      </c>
+      <c r="C15" t="str">
+        <v/>
+      </c>
+      <c r="D15" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E15" t="str">
+        <v>High</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2026-07-10</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -755,7 +755,7 @@
         <v>Just below state park to bottom of rotunda</v>
       </c>
       <c r="I12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="13">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -842,7 +842,7 @@
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -610,7 +610,7 @@
         <v>For research and overall knowledge of canals</v>
       </c>
       <c r="I7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="8">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -845,9 +845,38 @@
         <v>Yes</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>mrjd7hpjqtilb</v>
+      </c>
+      <c r="B16" t="str">
+        <v>FGCU Papers</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Complete drafts of Deep Learning Paper, Drone Paper, any other manuscript</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="E16" t="str">
+        <v>High</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="G16" t="str">
+        <v>When Time Allows</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -874,9 +874,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>mrjo4ps83tb44</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Text Taylor's Dad</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="E17" t="str">
+        <v>High</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -903,9 +903,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>mrjo52ghklych</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Schedule Sci Team Meeting</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E18" t="str">
+        <v>High</v>
+      </c>
+      <c r="F18" t="str">
+        <v>2026-07-13</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2026-07-14</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -900,7 +900,7 @@
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="18">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -639,7 +639,7 @@
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="9">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -932,9 +932,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>mrm3deyztugvz</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Explore hydrology tools</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Look at the arcgis pro</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F19" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="11">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -929,7 +929,7 @@
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="19">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -961,9 +961,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>mrm9tlmkub4m7</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Survey123 Check In Map Research</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Look into Survey123 for a potential check-in map for the residents of the Science Symposium so I can pull it up live and have it overlaid in a dashboard that we can put on the screen.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Low</v>
+      </c>
+      <c r="F20" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2026-07-29</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Can look into putting other layers in the map, like distance among canal, maybe flushing model if that is complete.</v>
+      </c>
+      <c r="I20" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -990,9 +990,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>mrma700w2xvr9</v>
+      </c>
+      <c r="B21" t="str">
+        <v>NCEAS Website Addition</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Something on the website with the NCEAS researchers with headshots, bios, etc.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F21" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Make it interactive and engaging</v>
+      </c>
+      <c r="I21" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1019,9 +1019,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>mrmghxvrxh6rd</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Distance Map with WQ Data on Marco</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Explore the relationship of points with water quality data and where they are in the canals vs open bay on Marco Island. Prepare a small analysis.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2026-07-15</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="14">
@@ -813,7 +813,7 @@
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="15">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1048,9 +1048,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>mrntjjhtceg64</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Test the Water Workshop Planning</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E23" t="str">
+        <v>High</v>
+      </c>
+      <c r="F23" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1077,9 +1077,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>mrntsxk6mc8b0</v>
+      </c>
+      <c r="B24" t="str">
+        <v>GitHub Host</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E24" t="str">
+        <v>High</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I24"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -523,7 +523,7 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="5">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1106,9 +1106,38 @@
         <v>No</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>mrp0df6jwrdp5</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Promote Workshop to Peers</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F25" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2026-07-17</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1074,7 +1074,7 @@
         <v/>
       </c>
       <c r="I23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="24">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="I24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
     </row>
     <row r="25">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:J25"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -408,6 +408,7 @@
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" customWidth="1"/>
     <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,6 +439,9 @@
       <c r="I1" t="str">
         <v>Completed</v>
       </c>
+      <c r="J1" t="str">
+        <v>Completed Date</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -467,6 +471,9 @@
       <c r="I2" t="str">
         <v>Yes</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -496,6 +503,9 @@
       <c r="I3" t="str">
         <v>No</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -525,6 +535,9 @@
       <c r="I4" t="str">
         <v>Yes</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -554,6 +567,9 @@
       <c r="I5" t="str">
         <v>No</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -583,6 +599,9 @@
       <c r="I6" t="str">
         <v>No</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -612,6 +631,9 @@
       <c r="I7" t="str">
         <v>Yes</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -641,6 +663,9 @@
       <c r="I8" t="str">
         <v>Yes</v>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -670,6 +695,9 @@
       <c r="I9" t="str">
         <v>No</v>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -699,6 +727,9 @@
       <c r="I10" t="str">
         <v>Yes</v>
       </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -728,6 +759,9 @@
       <c r="I11" t="str">
         <v>No</v>
       </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -757,6 +791,9 @@
       <c r="I12" t="str">
         <v>Yes</v>
       </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -786,6 +823,9 @@
       <c r="I13" t="str">
         <v>Yes</v>
       </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -815,6 +855,9 @@
       <c r="I14" t="str">
         <v>Yes</v>
       </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -844,6 +887,9 @@
       <c r="I15" t="str">
         <v>Yes</v>
       </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -873,6 +919,9 @@
       <c r="I16" t="str">
         <v>No</v>
       </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -902,6 +951,9 @@
       <c r="I17" t="str">
         <v>Yes</v>
       </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -931,6 +983,9 @@
       <c r="I18" t="str">
         <v>Yes</v>
       </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -960,6 +1015,9 @@
       <c r="I19" t="str">
         <v>No</v>
       </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -989,6 +1047,9 @@
       <c r="I20" t="str">
         <v>No</v>
       </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1018,6 +1079,9 @@
       <c r="I21" t="str">
         <v>No</v>
       </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -1047,6 +1111,9 @@
       <c r="I22" t="str">
         <v>No</v>
       </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -1076,6 +1143,9 @@
       <c r="I23" t="str">
         <v>Yes</v>
       </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -1105,6 +1175,9 @@
       <c r="I24" t="str">
         <v>Yes</v>
       </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -1126,7 +1199,7 @@
         <v>2026-07-17</v>
       </c>
       <c r="G25" t="str">
-        <v>2026-07-17</v>
+        <v>2026-07-20</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1134,10 +1207,13 @@
       <c r="I25" t="str">
         <v>No</v>
       </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1211,9 +1211,41 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>mrtatb9rkozj8</v>
+      </c>
+      <c r="B26" t="str">
+        <v>WQ Workshop 1-Pager</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Professional</v>
+      </c>
+      <c r="E26" t="str">
+        <v>High</v>
+      </c>
+      <c r="F26" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2026-07-20</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>No</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1237,10 +1237,10 @@
         <v/>
       </c>
       <c r="I26" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>2026-07-20</v>
       </c>
     </row>
   </sheetData>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -1077,10 +1077,10 @@
         <v>Make it interactive and engaging</v>
       </c>
       <c r="I21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>2026-07-21</v>
       </c>
     </row>
     <row r="22">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -480,7 +480,7 @@
         <v>mrdmr7v8ss585</v>
       </c>
       <c r="B3" t="str">
-        <v>Doctor and Dentist Appointments Scheduled</v>
+        <v>Dentist Appointments Scheduled</v>
       </c>
       <c r="C3" t="str">
         <v>Schedule doctor and dentist appointments. Bloodwork for Factor 5 and cavity are priorities</v>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -501,10 +501,10 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>2026-07-21</v>
       </c>
     </row>
     <row r="4">

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1243,9 +1243,41 @@
         <v>2026-07-20</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>mruvgtbvujkxp</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Doctor Appointment Scheduled</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Personal</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="F27" t="str">
+        <v>2026-07-21</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2026-07-31</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>No</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J27"/>
   </ignoredErrors>
 </worksheet>
 </file>